--- a/outputs/miq-import/miq_stars_import_ready.xlsx
+++ b/outputs/miq-import/miq_stars_import_ready.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="attestasiya_import" sheetId="1" r:id="Rdaf4c73b34dd4c08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="attestasiya_import" sheetId="1" r:id="Rb9c1605f4697443f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -439,16 +439,16 @@
         <x:v>Fatimə Quliyeva Mürşüd qızı</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>14.5313</x:v>
+        <x:v>16.6875</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>19.375</x:v>
+        <x:v>22.25</x:v>
       </x:c>
       <x:c r="E10" s="9" t="str">
         <x:v>2, 21</x:v>
       </x:c>
       <x:c r="F10" s="9" t="str">
-        <x:v>2 sətirin ədədi ortası</x:v>
+        <x:v>Dil 40 + ədəbiyyat 20×2; ədədi orta</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -654,7 +654,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6fa2a165a9543c2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc28183694fc645b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>